--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G475"/>
+  <dimension ref="A1:G477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13255,6 +13255,60 @@
       <c r="G475" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="C476" t="n">
+        <v>295.63</v>
+      </c>
+      <c r="D476" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="E476" t="n">
+        <v>289.88</v>
+      </c>
+      <c r="F476" t="n">
+        <v>254.71</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="C477" t="n">
+        <v>290.92</v>
+      </c>
+      <c r="D477" t="n">
+        <v>300.7</v>
+      </c>
+      <c r="E477" t="n">
+        <v>287.92</v>
+      </c>
+      <c r="F477" t="n">
+        <v>245.49</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B611"/>
+  <dimension ref="A1:B613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19382,6 +19436,26 @@
       </c>
       <c r="B611" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -19550,28 +19624,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.459788097551448</v>
+        <v>1.493587451844869</v>
       </c>
       <c r="J2" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K2" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2547809299572188</v>
+        <v>0.2611520262768443</v>
       </c>
       <c r="M2" t="n">
-        <v>12.91299005942706</v>
+        <v>12.97964498415251</v>
       </c>
       <c r="N2" t="n">
-        <v>295.014888056528</v>
+        <v>300.0459039699078</v>
       </c>
       <c r="O2" t="n">
-        <v>17.17599743993134</v>
+        <v>17.32183315847107</v>
       </c>
       <c r="P2" t="n">
-        <v>271.0129547336263</v>
+        <v>270.6004930937746</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19628,28 +19702,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5189671448828749</v>
+        <v>0.5048652532810624</v>
       </c>
       <c r="J3" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K3" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1320815791241371</v>
+        <v>0.1253734602675386</v>
       </c>
       <c r="M3" t="n">
-        <v>7.304106007374088</v>
+        <v>7.351380609737686</v>
       </c>
       <c r="N3" t="n">
-        <v>85.31892210540958</v>
+        <v>86.09916419787037</v>
       </c>
       <c r="O3" t="n">
-        <v>9.236824243505426</v>
+        <v>9.278963530366436</v>
       </c>
       <c r="P3" t="n">
-        <v>295.7268384461051</v>
+        <v>295.8970696641989</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19706,28 +19780,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5310230782486586</v>
+        <v>0.5252384338539408</v>
       </c>
       <c r="J4" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K4" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472469994416379</v>
+        <v>0.1452695084613734</v>
       </c>
       <c r="M4" t="n">
-        <v>7.037154605288613</v>
+        <v>7.042786191332048</v>
       </c>
       <c r="N4" t="n">
-        <v>78.72860801261699</v>
+        <v>78.59567681689533</v>
       </c>
       <c r="O4" t="n">
-        <v>8.872914290841369</v>
+        <v>8.865420284278423</v>
       </c>
       <c r="P4" t="n">
-        <v>294.7063271289896</v>
+        <v>294.776164862567</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19784,28 +19858,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3893585988231256</v>
+        <v>0.3811676866326398</v>
       </c>
       <c r="J5" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K5" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1221031313811202</v>
+        <v>0.1177574205933444</v>
       </c>
       <c r="M5" t="n">
-        <v>5.794587508231648</v>
+        <v>5.817490536742909</v>
       </c>
       <c r="N5" t="n">
-        <v>52.54667220970775</v>
+        <v>52.70633467396284</v>
       </c>
       <c r="O5" t="n">
-        <v>7.248908346068927</v>
+        <v>7.259912855810518</v>
       </c>
       <c r="P5" t="n">
-        <v>287.9655643285475</v>
+        <v>288.0644357027543</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19866,28 +19940,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.047200997662801</v>
+        <v>1.016385026927105</v>
       </c>
       <c r="J6" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K6" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09304261584279261</v>
+        <v>0.08797263734264837</v>
       </c>
       <c r="M6" t="n">
-        <v>18.19172737814321</v>
+        <v>18.29895780800825</v>
       </c>
       <c r="N6" t="n">
-        <v>512.3551970388645</v>
+        <v>515.5717895848771</v>
       </c>
       <c r="O6" t="n">
-        <v>22.63526445701186</v>
+        <v>22.70620597072257</v>
       </c>
       <c r="P6" t="n">
-        <v>257.6195098534452</v>
+        <v>257.992812666651</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19929,7 +20003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G475"/>
+  <dimension ref="A1:G477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37491,6 +37565,80 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-45.39153367338151,170.86395484147488</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-45.39086617828923,170.86327738630467</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-45.39089668786182,170.8622616406921</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-45.390833911614386,170.86129373447977</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-45.39063606937995,170.86031130959276</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>-45.39157993682434,170.86392781205345</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>-45.39082494260115,170.86329127867754</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-45.39086879344505,170.86226158112888</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-45.39081639683802,170.86129079894658</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-45.39055416592431,170.86029254793385</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G477"/>
+  <dimension ref="A1:G478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13207,50 +13207,50 @@
     <row r="474">
       <c r="A474" s="1" t="inlineStr">
         <is>
-          <t>2026-05-23 22:20:06+00:00</t>
+          <t>2026-06-09 22:13:17+00:00</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>338.57</v>
+        <v>313.9</v>
       </c>
       <c r="C474" t="n">
-        <v>308.55</v>
+        <v>301.76</v>
       </c>
       <c r="D474" t="n">
-        <v>308.9</v>
+        <v>307.15</v>
       </c>
       <c r="E474" t="n">
-        <v>293.05</v>
+        <v>291.53</v>
       </c>
       <c r="F474" t="n">
-        <v>272.71</v>
+        <v>263.39</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09 22:13:17+00:00</t>
+          <t>2026-06-25 22:13:32+00:00</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>341.08</v>
+        <v>315.28</v>
       </c>
       <c r="C475" t="n">
-        <v>301.76</v>
+        <v>295.63</v>
       </c>
       <c r="D475" t="n">
-        <v>307.15</v>
+        <v>303.8</v>
       </c>
       <c r="E475" t="n">
-        <v>291.53</v>
+        <v>289.88</v>
       </c>
       <c r="F475" t="n">
-        <v>263.39</v>
+        <v>254.71</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -13261,52 +13261,79 @@
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25 22:13:32+00:00</t>
+          <t>2026-07-19 22:13:52+00:00</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>346.13</v>
+        <v>315.77</v>
       </c>
       <c r="C476" t="n">
-        <v>295.63</v>
+        <v>290.92</v>
       </c>
       <c r="D476" t="n">
-        <v>303.8</v>
+        <v>300.7</v>
       </c>
       <c r="E476" t="n">
-        <v>289.88</v>
+        <v>287.92</v>
       </c>
       <c r="F476" t="n">
-        <v>254.71</v>
+        <v>245.49</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L9</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
         <is>
-          <t>2026-07-19 22:13:52+00:00</t>
+          <t>2026-08-04 22:14:24+00:00</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>351.69</v>
+        <v>315.77</v>
       </c>
       <c r="C477" t="n">
-        <v>290.92</v>
+        <v>290.65</v>
       </c>
       <c r="D477" t="n">
-        <v>300.7</v>
+        <v>299.77</v>
       </c>
       <c r="E477" t="n">
-        <v>287.92</v>
+        <v>287.78</v>
       </c>
       <c r="F477" t="n">
-        <v>245.49</v>
+        <v>242.78</v>
       </c>
       <c r="G477" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>306.35</v>
+      </c>
+      <c r="C478" t="n">
+        <v>290.64</v>
+      </c>
+      <c r="D478" t="n">
+        <v>299.59</v>
+      </c>
+      <c r="E478" t="n">
+        <v>288.19</v>
+      </c>
+      <c r="F478" t="n">
+        <v>242.78</v>
+      </c>
+      <c r="G478" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13323,7 +13350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B613"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19456,6 +19483,26 @@
       </c>
       <c r="B613" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -19624,28 +19671,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.493587451844869</v>
+        <v>1.441064202795519</v>
       </c>
       <c r="J2" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K2" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2611520262768443</v>
+        <v>0.2546773581081097</v>
       </c>
       <c r="M2" t="n">
-        <v>12.97964498415251</v>
+        <v>12.78489697852738</v>
       </c>
       <c r="N2" t="n">
-        <v>300.0459039699078</v>
+        <v>289.6302189561376</v>
       </c>
       <c r="O2" t="n">
-        <v>17.32183315847107</v>
+        <v>17.01852575742498</v>
       </c>
       <c r="P2" t="n">
-        <v>270.6004930937746</v>
+        <v>271.2402144069587</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19702,28 +19749,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5048652532810624</v>
+        <v>0.4889507916260077</v>
       </c>
       <c r="J3" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K3" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1253734602675386</v>
+        <v>0.1172186939483998</v>
       </c>
       <c r="M3" t="n">
-        <v>7.351380609737686</v>
+        <v>7.42700552008981</v>
       </c>
       <c r="N3" t="n">
-        <v>86.09916419787037</v>
+        <v>87.39099114783501</v>
       </c>
       <c r="O3" t="n">
-        <v>9.278963530366436</v>
+        <v>9.348314882792247</v>
       </c>
       <c r="P3" t="n">
-        <v>295.8970696641989</v>
+        <v>296.0899388615917</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19780,28 +19827,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5252384338539408</v>
+        <v>0.5172184989393518</v>
       </c>
       <c r="J4" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K4" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1452695084613734</v>
+        <v>0.1414900645288593</v>
       </c>
       <c r="M4" t="n">
-        <v>7.042786191332048</v>
+        <v>7.076254481420393</v>
       </c>
       <c r="N4" t="n">
-        <v>78.59567681689533</v>
+        <v>78.78573447344561</v>
       </c>
       <c r="O4" t="n">
-        <v>8.865420284278423</v>
+        <v>8.876132855779346</v>
       </c>
       <c r="P4" t="n">
-        <v>294.776164862567</v>
+        <v>294.8733366593868</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19858,28 +19905,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3811676866326398</v>
+        <v>0.3744301630724353</v>
       </c>
       <c r="J5" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K5" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1177574205933444</v>
+        <v>0.1138122705536502</v>
       </c>
       <c r="M5" t="n">
-        <v>5.817490536742909</v>
+        <v>5.843841122832172</v>
       </c>
       <c r="N5" t="n">
-        <v>52.70633467396284</v>
+        <v>52.98566713253102</v>
       </c>
       <c r="O5" t="n">
-        <v>7.259912855810518</v>
+        <v>7.279125437340054</v>
       </c>
       <c r="P5" t="n">
-        <v>288.0644357027543</v>
+        <v>288.1463122683318</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19940,28 +19987,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.016385026927105</v>
+        <v>0.9847226920397313</v>
       </c>
       <c r="J6" t="n">
+        <v>477</v>
+      </c>
+      <c r="K6" t="n">
         <v>476</v>
       </c>
-      <c r="K6" t="n">
-        <v>475</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08797263734264837</v>
+        <v>0.08230938860340598</v>
       </c>
       <c r="M6" t="n">
-        <v>18.29895780800825</v>
+        <v>18.44763804110714</v>
       </c>
       <c r="N6" t="n">
-        <v>515.5717895848771</v>
+        <v>521.7218555900284</v>
       </c>
       <c r="O6" t="n">
-        <v>22.70620597072257</v>
+        <v>22.84123148146852</v>
       </c>
       <c r="P6" t="n">
-        <v>257.992812666651</v>
+        <v>258.3783872856138</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20003,7 +20050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G477"/>
+  <dimension ref="A1:G478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37494,69 +37541,69 @@
     <row r="474">
       <c r="A474" s="1" t="inlineStr">
         <is>
-          <t>2026-05-23 22:20:06+00:00</t>
+          <t>2026-06-09 22:13:17+00:00</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>-45.39147076840032,170.8639915936371</t>
+          <t>-45.39126549503783,170.86411152372165</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>-45.39097929188443,170.86323927803033</t>
+          <t>-45.390919845964696,170.8632593055412</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>-45.390942578676245,170.8622617386823</t>
+          <t>-45.39092683182819,170.86226170505836</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>-45.39086223908413,170.8612984822588</t>
+          <t>-45.39084865619646,170.8612962057207</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>-45.39079596765725,170.8603479377043</t>
+          <t>-45.39071317588408,170.86032897245832</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09 22:13:17+00:00</t>
+          <t>2026-06-25 22:13:32+00:00</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>-45.39149165352127,170.8639793915396</t>
+          <t>-45.39127697770249,170.86410481504973</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>-45.390919845964696,170.8632593055412</t>
+          <t>-45.39086617828923,170.86327738630467</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>-45.39092683182819,170.86226170505836</t>
+          <t>-45.39089668786182,170.8622616406921</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>-45.39084865619646,170.8612962057207</t>
+          <t>-45.390833911614386,170.86129373447977</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>-45.39071317588408,170.86032897245832</t>
+          <t>-45.39063606937995,170.86031130959276</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -37568,72 +37615,109 @@
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25 22:13:32+00:00</t>
+          <t>2026-07-19 22:13:52+00:00</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>-45.39153367338151,170.86395484147488</t>
+          <t>-45.39128105488041,170.8641024329844</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>-45.39086617828923,170.86327738630467</t>
+          <t>-45.39082494260115,170.86329127867754</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>-45.39089668786182,170.8622616406921</t>
+          <t>-45.39086879344505,170.86226158112888</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>-45.390833911614386,170.86129373447977</t>
+          <t>-45.39081639683802,170.86129079894658</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>-45.39063606937995,170.86031130959276</t>
+          <t>-45.39055416592431,170.86029254793385</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L9</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
         <is>
-          <t>2026-07-19 22:13:52+00:00</t>
+          <t>2026-08-04 22:14:24+00:00</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>-45.39157993682434,170.86392781205345</t>
+          <t>-45.39128105488041,170.8641024329844</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>-45.39082494260115,170.86329127867754</t>
+          <t>-45.390822578771825,170.86329207505497</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>-45.39086879344505,170.86226158112888</t>
+          <t>-45.39086042511998,170.8622615632598</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>-45.39081639683802,170.86129079894658</t>
+          <t>-45.390815145782575,170.86129058926568</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>-45.39055416592431,170.86029254793385</t>
+          <t>-45.390530092348364,170.86028703339937</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>-45.391202673204816,170.8641482269135</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>-45.390822491222586,170.86329210455042</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-45.39085880544418,170.86226155980128</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-45.39081880958783,170.86129120333115</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-45.390530092348364,170.86028703339937</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G478"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13334,6 +13334,60 @@
         <v>242.78</v>
       </c>
       <c r="G478" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>302.81</v>
+      </c>
+      <c r="C479" t="n">
+        <v>291.16</v>
+      </c>
+      <c r="D479" t="n">
+        <v>299.78</v>
+      </c>
+      <c r="E479" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="F479" t="n">
+        <v>239.72</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>290.13</v>
+      </c>
+      <c r="C480" t="n">
+        <v>286.18</v>
+      </c>
+      <c r="D480" t="n">
+        <v>295.8</v>
+      </c>
+      <c r="E480" t="n">
+        <v>285.42</v>
+      </c>
+      <c r="F480" t="n">
+        <v>221.46</v>
+      </c>
+      <c r="G480" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13350,7 +13404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19503,6 +19557,26 @@
       </c>
       <c r="B615" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -19671,28 +19745,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.441064202795519</v>
+        <v>1.429070388635794</v>
       </c>
       <c r="J2" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K2" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2546773581081097</v>
+        <v>0.2525414858722042</v>
       </c>
       <c r="M2" t="n">
-        <v>12.78489697852738</v>
+        <v>12.80616469243087</v>
       </c>
       <c r="N2" t="n">
-        <v>289.6302189561376</v>
+        <v>289.367244246093</v>
       </c>
       <c r="O2" t="n">
-        <v>17.01852575742498</v>
+        <v>17.01079787211914</v>
       </c>
       <c r="P2" t="n">
-        <v>271.2402144069587</v>
+        <v>271.3876653047992</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19749,28 +19823,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4889507916260077</v>
+        <v>0.4712343071897977</v>
       </c>
       <c r="J3" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K3" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1172186939483998</v>
+        <v>0.1086647953011959</v>
       </c>
       <c r="M3" t="n">
-        <v>7.42700552008981</v>
+        <v>7.501513349966928</v>
       </c>
       <c r="N3" t="n">
-        <v>87.39099114783501</v>
+        <v>88.80844472586712</v>
       </c>
       <c r="O3" t="n">
-        <v>9.348314882792247</v>
+        <v>9.42382325417169</v>
       </c>
       <c r="P3" t="n">
-        <v>296.0899388615917</v>
+        <v>296.3052936535915</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19827,28 +19901,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5172184989393518</v>
+        <v>0.5077149190990617</v>
       </c>
       <c r="J4" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K4" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1414900645288593</v>
+        <v>0.1372856419483652</v>
       </c>
       <c r="M4" t="n">
-        <v>7.076254481420393</v>
+        <v>7.104196545959588</v>
       </c>
       <c r="N4" t="n">
-        <v>78.78573447344561</v>
+        <v>78.97870834027678</v>
       </c>
       <c r="O4" t="n">
-        <v>8.876132855779346</v>
+        <v>8.886996587164687</v>
       </c>
       <c r="P4" t="n">
-        <v>294.8733366593868</v>
+        <v>294.9888675873767</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19905,28 +19979,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3744301630724353</v>
+        <v>0.3643168995446887</v>
       </c>
       <c r="J5" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K5" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1138122705536502</v>
+        <v>0.1081913210262658</v>
       </c>
       <c r="M5" t="n">
-        <v>5.843841122832172</v>
+        <v>5.877263220696252</v>
       </c>
       <c r="N5" t="n">
-        <v>52.98566713253102</v>
+        <v>53.34161673603013</v>
       </c>
       <c r="O5" t="n">
-        <v>7.279125437340054</v>
+        <v>7.30353453719705</v>
       </c>
       <c r="P5" t="n">
-        <v>288.1463122683318</v>
+        <v>288.2692403612197</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19987,28 +20061,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9847226920397313</v>
+        <v>0.9377738204610712</v>
       </c>
       <c r="J6" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K6" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08230938860340598</v>
+        <v>0.07417104584738543</v>
       </c>
       <c r="M6" t="n">
-        <v>18.44763804110714</v>
+        <v>18.64832265852761</v>
       </c>
       <c r="N6" t="n">
-        <v>521.7218555900284</v>
+        <v>532.1199914407779</v>
       </c>
       <c r="O6" t="n">
-        <v>22.84123148146852</v>
+        <v>23.06772618705142</v>
       </c>
       <c r="P6" t="n">
-        <v>258.3783872856138</v>
+        <v>258.9511168923931</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20050,7 +20124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G478"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37723,6 +37797,80 @@
         </is>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-45.39117321766508,170.86416543606342</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-45.390827043782764,170.86329057078646</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-45.39086051510199,170.86226156345197</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-45.39081309047717,170.86129024478998</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-45.39050290963863,170.86028080666085</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-45.39106771022641,170.86422707772667</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-45.39078344426302,170.86330525951544</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-45.390824702269896,170.86226148697963</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-45.39079405656191,170.8612870546464</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-45.39034070169685,170.86024364983223</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
